--- a/datos.xlsx
+++ b/datos.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,6 +485,11 @@
           <t>COD_RESOLUCION_1_OTP</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>MODIFICAR_OTP</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -499,57 +504,104 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
+          <t>22871058
+22871058</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
           <t>22871058</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr"/>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>PROYECTOS</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr"/>
+      <c r="H2" s="1" t="inlineStr"/>
+      <c r="I2" s="1" t="inlineStr"/>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>TERCEROS</t>
+        </is>
+      </c>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>22871058</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>FIBRA OPTICA</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>22871058</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>22871058
+22871058</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>22871058</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr"/>
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>PROYECTOS</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t>INTERNET SEGURO CORPORATIVO</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr"/>
+      <c r="H3" s="1" t="inlineStr"/>
+      <c r="I3" s="1" t="inlineStr"/>
+      <c r="J3" s="1" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>TERCEROS</t>
+        </is>
+      </c>
+      <c r="N3" s="1" t="inlineStr">
         <is>
           <t>SI</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t>HABILITACIÓN SERVICIOS</t>
         </is>
       </c>
     </row>

--- a/datos.xlsx
+++ b/datos.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,6 +488,21 @@
       <c r="N1" t="inlineStr">
         <is>
           <t>MODIFICAR_OTP</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>TIPO</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>DOCUMENTACION_UM</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>CERRAR_OTH</t>
         </is>
       </c>
     </row>

--- a/datos.xlsx
+++ b/datos.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:U2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,120 +505,94 @@
           <t>CERRAR_OTH</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>DOCUMENTACION</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>DOC_CONFIG</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>OT_TIPO</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>ARCHIVO_PATH</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>22871058</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>22871058</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>22871058
-22871058</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>22871058</t>
-        </is>
-      </c>
+          <t>22615568</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr"/>
+      <c r="C2" s="1" t="inlineStr"/>
+      <c r="D2" s="1" t="inlineStr"/>
       <c r="E2" s="1" t="inlineStr"/>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>PROYECTOS</t>
-        </is>
-      </c>
+      <c r="F2" s="1" t="inlineStr"/>
       <c r="G2" s="1" t="inlineStr"/>
       <c r="H2" s="1" t="inlineStr"/>
       <c r="I2" s="1" t="inlineStr"/>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t>TERCEROS</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>22871058</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>22871058</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>22871058
-22871058</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>22871058</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr"/>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>PROYECTOS</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr"/>
-      <c r="H3" s="1" t="inlineStr"/>
-      <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="M3" s="1" t="inlineStr">
-        <is>
-          <t>TERCEROS</t>
-        </is>
-      </c>
-      <c r="N3" s="1" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="J2" s="1" t="inlineStr"/>
+      <c r="K2" s="1" t="inlineStr"/>
+      <c r="L2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr"/>
+      <c r="N2" s="1" t="inlineStr"/>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t>CONFIGURACION</t>
+        </is>
+      </c>
+      <c r="P2" s="1" t="inlineStr"/>
+      <c r="Q2" s="1" t="inlineStr"/>
+      <c r="R2" s="1" t="inlineStr">
+        <is>
+          <t>*********   CHECK LIST DE CONFIGURACIÓN *********				
+**Requerimientos para configuración**				
+TIPO DE ORDEN	NOVEDADES	$Cambio de Servicio		
+TIPO DE SERVICIO	DATOS	MPLS INTRANET		
+ANCHO DE BANDA	20MB			
+OTP ASOCIADAS	N/A			
+OTP de entrega de Ultima Milla/ ID UM servicio actual:	22615568 // WGROU13			
+TIPO UM	EXISTENTE			
+***INFORMACION DE ENTREGA DE ULTIMA MILLA ****	SE SOLICITA CONFIGURACION PARA CAMBIO DE SERVICO DE MPLS POR BANDA ANCHACON UN BW DE 25MB			
+ANCHO DE BANDA  &gt;  100 MEGAS ?	NO			
+RESPUESTA FACTIBILIDAD BW &gt; 100 MEGAS				
+Fecha requerida de configuración:				
+"Revisar modulo SFP en el puerto (Aplica para canales mayores a 100M)"				
+Si requiere Demarcador Documentar el tipo de demarcador a instalar				
+Adjuntar en OTP soportes requeridos para entrega:				
+**Plan de Trabajo				
+Aseguramiento al proceso				
+"Nombre Ingeniero IS a cargo en caso de Escalamiento de Configuración"				
+Documentación adjunta para configuración:				
+* DATOS GESTION DE CPE*				
+Marca de CPE o Router a Instalar				
+* DATOS CLIENTE ENVIO REPORTE GESTION PROACTIVA *				
+Cliente especial?				
+Campo para cliente Cliente especial - Documente el Alias de la sede				
+NDS				
+NOMBRE 				
+CORREO ELECTRONICO A DONDE SE DEBE ENVIAR INFORME				
+NOMBRE DE INFORME				
+FRECUENCIA DE ENVIO DEL INFORME				
+CONFIRMA UN DIA Y HORA ESPECIFICO PARA EL ENVIO DEL INFORME?0BSERVACIONES	SE SOLICITA CONFIGURACION PARA CAMBIO DE SERVICO DE MPLS POR BANDA ANCHA CON UN BW DE 25MB</t>
+        </is>
+      </c>
+      <c r="S2" s="1" t="inlineStr"/>
+      <c r="T2" s="1" t="inlineStr">
+        <is>
+          <t>OT CORTA</t>
+        </is>
+      </c>
+      <c r="U2" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/datos.xlsx
+++ b/datos.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,94 +505,120 @@
           <t>CERRAR_OTH</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>DOCUMENTACION</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>DOC_CONFIG</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>OT_TIPO</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>ARCHIVO_PATH</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>22615568</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr"/>
-      <c r="C2" s="1" t="inlineStr"/>
-      <c r="D2" s="1" t="inlineStr"/>
+          <t>22871058</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>22871058</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>22871058
+22871058</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>22871058</t>
+        </is>
+      </c>
       <c r="E2" s="1" t="inlineStr"/>
-      <c r="F2" s="1" t="inlineStr"/>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>PROYECTOS</t>
+        </is>
+      </c>
       <c r="G2" s="1" t="inlineStr"/>
       <c r="H2" s="1" t="inlineStr"/>
       <c r="I2" s="1" t="inlineStr"/>
-      <c r="J2" s="1" t="inlineStr"/>
-      <c r="K2" s="1" t="inlineStr"/>
-      <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
-      <c r="N2" s="1" t="inlineStr"/>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t>CONFIGURACION</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr"/>
-      <c r="Q2" s="1" t="inlineStr"/>
-      <c r="R2" s="1" t="inlineStr">
-        <is>
-          <t>*********   CHECK LIST DE CONFIGURACIÓN *********				
-**Requerimientos para configuración**				
-TIPO DE ORDEN	NOVEDADES	$Cambio de Servicio		
-TIPO DE SERVICIO	DATOS	MPLS INTRANET		
-ANCHO DE BANDA	20MB			
-OTP ASOCIADAS	N/A			
-OTP de entrega de Ultima Milla/ ID UM servicio actual:	22615568 // WGROU13			
-TIPO UM	EXISTENTE			
-***INFORMACION DE ENTREGA DE ULTIMA MILLA ****	SE SOLICITA CONFIGURACION PARA CAMBIO DE SERVICO DE MPLS POR BANDA ANCHACON UN BW DE 25MB			
-ANCHO DE BANDA  &gt;  100 MEGAS ?	NO			
-RESPUESTA FACTIBILIDAD BW &gt; 100 MEGAS				
-Fecha requerida de configuración:				
-"Revisar modulo SFP en el puerto (Aplica para canales mayores a 100M)"				
-Si requiere Demarcador Documentar el tipo de demarcador a instalar				
-Adjuntar en OTP soportes requeridos para entrega:				
-**Plan de Trabajo				
-Aseguramiento al proceso				
-"Nombre Ingeniero IS a cargo en caso de Escalamiento de Configuración"				
-Documentación adjunta para configuración:				
-* DATOS GESTION DE CPE*				
-Marca de CPE o Router a Instalar				
-* DATOS CLIENTE ENVIO REPORTE GESTION PROACTIVA *				
-Cliente especial?				
-Campo para cliente Cliente especial - Documente el Alias de la sede				
-NDS				
-NOMBRE 				
-CORREO ELECTRONICO A DONDE SE DEBE ENVIAR INFORME				
-NOMBRE DE INFORME				
-FRECUENCIA DE ENVIO DEL INFORME				
-CONFIRMA UN DIA Y HORA ESPECIFICO PARA EL ENVIO DEL INFORME?0BSERVACIONES	SE SOLICITA CONFIGURACION PARA CAMBIO DE SERVICO DE MPLS POR BANDA ANCHA CON UN BW DE 25MB</t>
-        </is>
-      </c>
-      <c r="S2" s="1" t="inlineStr"/>
-      <c r="T2" s="1" t="inlineStr">
-        <is>
-          <t>OT CORTA</t>
-        </is>
-      </c>
-      <c r="U2" s="1" t="inlineStr"/>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>TERCEROS</t>
+        </is>
+      </c>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>22871058</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>22871058</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>22871058
+22871058</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>22871058</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr"/>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>PROYECTOS</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr"/>
+      <c r="H3" s="1" t="inlineStr"/>
+      <c r="I3" s="1" t="inlineStr"/>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>TERCEROS</t>
+        </is>
+      </c>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/datos.xlsx
+++ b/datos.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:Y2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,14 +522,34 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>ARCHIVO_PATH</t>
+          <t>PATH_PRUEBAS_PREVIAS</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>PATH_MINUTOGRAMA</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>PATH_VALIDACION_WAN_LAN</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>PATH_SCRIPT</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>PATH_SATURACION</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>22615568</t>
+          <t>22661495</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr"/>
@@ -540,7 +560,11 @@
       <c r="G2" s="1" t="inlineStr"/>
       <c r="H2" s="1" t="inlineStr"/>
       <c r="I2" s="1" t="inlineStr"/>
-      <c r="J2" s="1" t="inlineStr"/>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
       <c r="K2" s="1" t="inlineStr"/>
       <c r="L2" s="1" t="inlineStr"/>
       <c r="M2" s="1" t="inlineStr"/>
@@ -554,45 +578,40 @@
       <c r="Q2" s="1" t="inlineStr"/>
       <c r="R2" s="1" t="inlineStr">
         <is>
-          <t>*********   CHECK LIST DE CONFIGURACIÓN *********				
-**Requerimientos para configuración**				
-TIPO DE ORDEN	NOVEDADES	$Cambio de Servicio		
-TIPO DE SERVICIO	DATOS	MPLS INTRANET		
-ANCHO DE BANDA	20MB			
-OTP ASOCIADAS	N/A			
-OTP de entrega de Ultima Milla/ ID UM servicio actual:	22615568 // WGROU13			
-TIPO UM	EXISTENTE			
-***INFORMACION DE ENTREGA DE ULTIMA MILLA ****	SE SOLICITA CONFIGURACION PARA CAMBIO DE SERVICO DE MPLS POR BANDA ANCHACON UN BW DE 25MB			
-ANCHO DE BANDA  &gt;  100 MEGAS ?	NO			
-RESPUESTA FACTIBILIDAD BW &gt; 100 MEGAS				
-Fecha requerida de configuración:				
-"Revisar modulo SFP en el puerto (Aplica para canales mayores a 100M)"				
-Si requiere Demarcador Documentar el tipo de demarcador a instalar				
-Adjuntar en OTP soportes requeridos para entrega:				
-**Plan de Trabajo				
-Aseguramiento al proceso				
-"Nombre Ingeniero IS a cargo en caso de Escalamiento de Configuración"				
-Documentación adjunta para configuración:				
-* DATOS GESTION DE CPE*				
-Marca de CPE o Router a Instalar				
-* DATOS CLIENTE ENVIO REPORTE GESTION PROACTIVA *				
-Cliente especial?				
-Campo para cliente Cliente especial - Documente el Alias de la sede				
-NDS				
-NOMBRE 				
-CORREO ELECTRONICO A DONDE SE DEBE ENVIAR INFORME				
-NOMBRE DE INFORME				
-FRECUENCIA DE ENVIO DEL INFORME				
-CONFIRMA UN DIA Y HORA ESPECIFICO PARA EL ENVIO DEL INFORME?0BSERVACIONES	SE SOLICITA CONFIGURACION PARA CAMBIO DE SERVICO DE MPLS POR BANDA ANCHA CON UN BW DE 25MB</t>
+          <t>22661495</t>
         </is>
       </c>
       <c r="S2" s="1" t="inlineStr"/>
       <c r="T2" s="1" t="inlineStr">
         <is>
-          <t>OT CORTA</t>
-        </is>
-      </c>
-      <c r="U2" s="1" t="inlineStr"/>
+          <t>OT LARGA</t>
+        </is>
+      </c>
+      <c r="U2" s="1" t="inlineStr">
+        <is>
+          <t>C:\Users\dell\Desktop\kickoff\project-Auto-bot\OLE\22661495_aaaaak0499_-_previas.txt</t>
+        </is>
+      </c>
+      <c r="V2" s="1" t="inlineStr">
+        <is>
+          <t>C:\Users\dell\Desktop\kickoff\project-Auto-bot\OLE\22661495_minutograma_saturacion.xls</t>
+        </is>
+      </c>
+      <c r="W2" s="1" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="X2" s="1" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Y2" s="1" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/datos.xlsx
+++ b/datos.xlsx
@@ -46,11 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -416,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y2"/>
+  <dimension ref="A1:Y1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,73 +540,6 @@
       <c r="Y1" t="inlineStr">
         <is>
           <t>PATH_SATURACION</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>22661495</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr"/>
-      <c r="C2" s="1" t="inlineStr"/>
-      <c r="D2" s="1" t="inlineStr"/>
-      <c r="E2" s="1" t="inlineStr"/>
-      <c r="F2" s="1" t="inlineStr"/>
-      <c r="G2" s="1" t="inlineStr"/>
-      <c r="H2" s="1" t="inlineStr"/>
-      <c r="I2" s="1" t="inlineStr"/>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>COMPLETADO</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr"/>
-      <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
-      <c r="N2" s="1" t="inlineStr"/>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t>CONFIGURACION</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr"/>
-      <c r="Q2" s="1" t="inlineStr"/>
-      <c r="R2" s="1" t="inlineStr">
-        <is>
-          <t>22661495</t>
-        </is>
-      </c>
-      <c r="S2" s="1" t="inlineStr"/>
-      <c r="T2" s="1" t="inlineStr">
-        <is>
-          <t>OT LARGA</t>
-        </is>
-      </c>
-      <c r="U2" s="1" t="inlineStr">
-        <is>
-          <t>C:\Users\dell\Desktop\kickoff\project-Auto-bot\OLE\22661495_aaaaak0499_-_previas.txt</t>
-        </is>
-      </c>
-      <c r="V2" s="1" t="inlineStr">
-        <is>
-          <t>C:\Users\dell\Desktop\kickoff\project-Auto-bot\OLE\22661495_minutograma_saturacion.xls</t>
-        </is>
-      </c>
-      <c r="W2" s="1" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="X2" s="1" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Y2" s="1" t="inlineStr">
-        <is>
-          <t>NO</t>
         </is>
       </c>
     </row>
